--- a/media/price_lists/duna_srl.xlsx
+++ b/media/price_lists/duna_srl.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="api_import" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,1689 +425,6245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>supplier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>parser_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>title_original</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>price_original</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dollar_rate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>price_ars</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>price_wholesale_final</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>RFKH01-6.0-22</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Sin Compensador R22 1/2" Rosca Sanhua</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>66239</v>
+      <c r="F2" t="n">
+        <v>66938</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>66938.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>83003.12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>RFKH01E-6.0-13</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Con Compensador R22 1/2" Rosca Sanhua</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>67318</v>
+      <c r="F3" t="n">
+        <v>68029</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>68029.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>84355.96</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>RFKH03-4.8-21</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Sin Compensador R404 1/2" Rosca Sanhua</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>66241</v>
+      <c r="F4" t="n">
+        <v>66940</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>66940.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>83005.60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>RFKH03E-4.8-10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Con compensador R404 1/2" Soldar Sanhua</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>58527</v>
+      <c r="F5" t="n">
+        <v>59145</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>59145.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>73339.80</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>RFKH03E-4.8-15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Con Compensador R404 1/2" Rosca Sanhua</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>67318</v>
+      <c r="F6" t="n">
+        <v>68029</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>68029.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>84355.96</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>RFKH-023-00</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 00</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>10498</v>
+      <c r="F7" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>RFKH-023-01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 01</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>10498</v>
+      <c r="F8" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>RFKH-023-02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 02</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>10498</v>
+      <c r="F9" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>RFKH-023-03</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 03</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>10498</v>
+      <c r="F10" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>RFKH-023-04</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 04</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>10498</v>
+      <c r="F11" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>RFKH-023-05</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 05</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>10498</v>
+      <c r="F12" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>RFKH-023-06</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Tobera para válvula de expansión Sanhua Nº 06</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>10498</v>
+      <c r="F13" t="n">
+        <v>10609</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10609.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13155.16</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>RFKH04E-2.9-19</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Válvula de Expansión Termostática Con Compensador R134a 1/2" Rosca Sanhua</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>67318</v>
+      <c r="F14" t="n">
+        <v>68029</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>68029.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>84355.96</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>SBV02-319T</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Válvula de Bola 1/4" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>34092</v>
-      </c>
+      <c r="F15" t="n">
+        <v>34452</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>34452.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>42720.48</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>SBV03-319T</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Válvula de Bola 3/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>34226</v>
+      <c r="F16" t="n">
+        <v>34588</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>34588.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>42889.12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>SBV04-319T</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Válvula de Bola 1/2" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>34926</v>
+      <c r="F17" t="n">
+        <v>35295</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>35295.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>43765.80</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>SSV-A2GSHC-23</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Válvula Split - Robinete - de Servicio 1/4" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>10697</v>
-      </c>
+      <c r="F18" t="n">
+        <v>10810</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10810.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>13404.40</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>SSV-JA3GSHC-20</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Válvula Split - Robinete - de Servicio 3/8" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>14601</v>
+      <c r="F19" t="n">
+        <v>14755</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>14755.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18296.20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>SSV-JA4GSCH-19</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Válvula Split - Robinete - de Servicio 1/2" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>18801</v>
+      <c r="F20" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>19000.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>23560.00</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>SSV-JA5GSHC-15</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Válvula Split o Robinete 5/8" Soldable - Servicio - Sanhua</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>24589</v>
+      <c r="F21" t="n">
+        <v>24849</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>24849.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30812.76</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>SSV-JA6GSHC-13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Válvula Split - Robinete - de Servicio 3/4" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>36328</v>
+      <c r="F22" t="n">
+        <v>36711</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>36711.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>45521.64</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>MDF-A03-10H004</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Válvula Solenoide 5/8" 220V Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>73618</v>
+      <c r="F23" t="n">
+        <v>74396</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>74396.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>92251.04</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>MDF-A03-10L002</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Válvula Solenoide 5/8" 220V Rosca - Sanhua</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>80053</v>
+      <c r="F24" t="n">
+        <v>80899</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>80899.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>100314.76</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>MDF-A03-15H004</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Válvula Solenoide 7/8" 220V Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>170166</v>
+      <c r="F25" t="n">
+        <v>171963</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>171963.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>213234.12</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>MDF-A03-3L004</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Válvula Solenoide 3/8" 220V Rosca - Sanhua</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>37924</v>
+      <c r="F26" t="n">
+        <v>38325</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>38325.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>47523.00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>MDF-A03-6H004</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Válvula Solenoide 1/2" 220V Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>58099</v>
+      <c r="F27" t="n">
+        <v>58713</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>58713.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>72804.12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>MDF-A03-6L004</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Válvula Solenoide 1/2" 220V Rosca - Sanhua</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>49927</v>
-      </c>
+      <c r="F28" t="n">
+        <v>50455</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50455.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>62564.20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>SHF(L)-7H-34U-52</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Válvula Inversora 4 Vías Entrada 3/8" - Salida 1/2" Sanhua</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>34293</v>
+      <c r="F29" t="n">
+        <v>34656</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>34656.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>42973.44</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>SHF(L)-11H-45D1-52</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Válvula Inversora 4 Vías Entrada 1/2" - Salida 5/8" Sanhua</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>46365</v>
+      <c r="F30" t="n">
+        <v>46854</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>46854.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>58098.96</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>SHF-20D-46-02(P)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Válvula Inversora 4 Vías Entrada 1/2" - Salida 3/4" Sanhua</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>66851</v>
+      <c r="F31" t="n">
+        <v>67557</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>67557.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>83770.68</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>CTF16H01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 5/8" de Evaporación - Sanhua</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>107443</v>
+      <c r="F32" t="n">
+        <v>108578</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>108578.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>134636.72</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>XTF12H01</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 1/2" de Succión - Sanhua</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>91024</v>
+      <c r="F33" t="n">
+        <v>91986</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>91986.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>114062.64</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>XTF15H01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 5/8" de Succión Sanhua</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>93200</v>
+      <c r="F34" t="n">
+        <v>94185</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>94185.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>116789.40</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>XTF22H01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 7/8" de Succión Sanhua</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>93914</v>
+      <c r="F35" t="n">
+        <v>94907</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>94907.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>117684.68</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>ACM-P21076-901</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Acumulador de Succión 5/8" Sanhua</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>47491</v>
+      <c r="F36" t="n">
+        <v>47993</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>47993.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>59511.32</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>HTG-A00-010001</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Núcleo Filtrante de reemplazo | Máxima Deshidratación 100% Tamiz Molecular Sanhua</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>26143</v>
+      <c r="F37" t="n">
+        <v>26419</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>26419.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32759.56</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>HTG-A80-010001</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Núcleo Filtrante de Reemplazo | Deshidratador para Humedad y Acidos Sanhua</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>26143</v>
+      <c r="F38" t="n">
+        <v>26419</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>26419.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>32759.56</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>HTG-B00-010002</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Núcleo Filtrante de Reemplazo | Deshidratador Mecánico para Partículas y Humedad Sanhua</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>40558</v>
+      <c r="F39" t="n">
+        <v>40987</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40987.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>50823.88</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>XTF28H01</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 1.1/8" de Succión Sanhua</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>136563</v>
+      <c r="F40" t="n">
+        <v>138006</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>138006.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>171127.44</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>XTF35H01</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Válvula Reguladora de Presión 1.3/8" de Succión Sanhua</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>137762</v>
+      <c r="F41" t="n">
+        <v>139218</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>139218.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>172630.32</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>DTGE032S</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/4" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>10042</v>
+      <c r="F42" t="n">
+        <v>10148</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10148.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12583.52</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>DTGE082</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Filtro Deshidratador / Secador 1/4" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>21681</v>
+      <c r="F43" t="n">
+        <v>21910</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21910.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>27168.40</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>DTGE082S</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/4" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>17164</v>
+      <c r="F44" t="n">
+        <v>17345</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>17345.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>21507.80</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>DTGE083</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 3/8" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>21736</v>
+      <c r="F45" t="n">
+        <v>21966</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>21966.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>27237.84</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>DTGE083S</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 3/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>17497</v>
+      <c r="F46" t="n">
+        <v>17682</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17682.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>21925.68</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>DTGE162</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/4" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>22457</v>
+      <c r="F47" t="n">
+        <v>22695</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>22695.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>28141.80</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>DTGE162S</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/4" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>18024</v>
+      <c r="F48" t="n">
+        <v>18214</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18214.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>22585.36</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>DTGE163</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 3/8" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>23040</v>
+      <c r="F49" t="n">
+        <v>23283</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>23283.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>28870.92</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>DTGE163S</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 3/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>18106</v>
+      <c r="F50" t="n">
+        <v>18297</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>18297.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>22688.28</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>DTGE164</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/2" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>24591</v>
+      <c r="F51" t="n">
+        <v>24851</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>24851.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>30815.24</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>DTGE164S</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/2" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>18190</v>
+      <c r="F52" t="n">
+        <v>18382</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>18382.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>22793.68</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>DTGE165</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 5/8" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>26420</v>
+      <c r="F53" t="n">
+        <v>26699</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>26699.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>33106.76</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>DTGE165S</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 5/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>18273</v>
+      <c r="F54" t="n">
+        <v>18466</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18466.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22897.84</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>DTGE303S</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 3/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>26699</v>
+      <c r="F55" t="n">
+        <v>26981</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>26981.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33456.44</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>DTGE304</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/2" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>33932</v>
+      <c r="F56" t="n">
+        <v>34290</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>34290.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>42519.60</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>DTGE304S</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 1/2" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>27419</v>
+      <c r="F57" t="n">
+        <v>27708</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>27708.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>34357.92</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>DTGE305</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 5/8" Roscable Sanhua</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>35595</v>
+      <c r="F58" t="n">
+        <v>35971</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>35971.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>44604.04</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>DTGE305S</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Filtro Deshidratador - Filtro Secador 5/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>28223</v>
+      <c r="F59" t="n">
+        <v>28521</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>28521.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>35366.04</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>HTG04811S</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 1-3/8" (35 mm) Sanhua</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>155789</v>
+      <c r="F60" t="n">
+        <v>157435</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>157435.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>195219.40</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>HTG04813S</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 1-5/8" Sanhua</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>155441</v>
+      <c r="F61" t="n">
+        <v>157083</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>157083.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>194782.92</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>HTG04817S</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 2-1/8" (54 mm) Sanhua</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>180657</v>
+      <c r="F62" t="n">
+        <v>182565</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>182565.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>226380.60</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>HTG04821S</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 2-5/8" Sanhua</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>194576</v>
+      <c r="F63" t="n">
+        <v>196632</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>196632.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>243823.68</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>HTG0485S</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 5/8" (16 mm) Sanhua</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>155789</v>
+      <c r="F64" t="n">
+        <v>157435</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>157435.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>195219.40</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>HTG0487S</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 7/8" (22 mm) Sanhua</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>155789</v>
+      <c r="F65" t="n">
+        <v>157435</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>157435.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>195219.40</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>HTG0489S</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Carcasa Porta Núcleos - Filtro Deshidratador 1-1/8" Sanhua</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>155789</v>
+      <c r="F66" t="n">
+        <v>157435</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>157435.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>195219.40</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>LRA-C02127-901</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Tubo Recibidor de Líquido 3.3 Litros Sanhua</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>123353</v>
+      <c r="F67" t="n">
+        <v>124656</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>124656.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>154573.44</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>LRA-C03153-901</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Tubo Recibidor de Líquido 5.2 Litros Sanhua</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>154970</v>
+      <c r="F68" t="n">
+        <v>156607</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>156607.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>194192.68</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>LRA-C04153-901</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Tubo Recibidor de Líquido 6.8 Litros Sanhua</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>167891</v>
+      <c r="F69" t="n">
+        <v>169664</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>169664.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>210383.36</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>LRA-C05153-901</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Tubo Recibidor de Líquido 7.7 Litros Sanhua</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>175431</v>
+      <c r="F70" t="n">
+        <v>177284</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>177284.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>219832.16</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>LRA-C06153-901</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Tubo Recibidor de Líquido 9.9 Litros Sanhua</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>204865</v>
+      <c r="F71" t="n">
+        <v>207029</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>207029.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>256715.96</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>YFQ-F00101-002</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Separador de Aceite 1/2" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>125469</v>
+      <c r="F72" t="n">
+        <v>126794</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>126794.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>157224.56</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>SYJ06L01</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Visor de Líquido 1/4" Roscable - Sanhua</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>18854</v>
-      </c>
+      <c r="F73" t="n">
+        <v>19053</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>19053.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>23625.72</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>SYJ10H01</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Visor de Líquido 3/8" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>21182</v>
-      </c>
+      <c r="F74" t="n">
+        <v>21406</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>21406.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>26543.44</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>SYJ12H01</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Visor de Líquido 1/2" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>28000</v>
-      </c>
+      <c r="F75" t="n">
+        <v>28296</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>28296.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>35087.04</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>SYJ16H01</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Visor de Líquido 5/8" Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>29443</v>
+      <c r="F76" t="n">
+        <v>29754</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>29754.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>36894.96</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>MQ-A0322G-000001</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Bobina para Válvula Solenoide 220-240V IP67 Sanhua</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>27199</v>
+      <c r="F77" t="n">
+        <v>27486</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>27486.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>34082.64</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>MQ-D03024-000002</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Bobina para Válvula Solenoide 24V Sanhua</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>29836</v>
+      <c r="F78" t="n">
+        <v>30151</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30151.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>37387.24</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>SYJ10L01</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Visor de Líquido 3/8" Roscable - Sanhua</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>25672</v>
-      </c>
+      <c r="F79" t="n">
+        <v>25944</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>25944.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>32170.56</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>SYJ12L01</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Visor de Líquido  1/2" Roscable - Sanhua</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>29386</v>
-      </c>
+      <c r="F80" t="n">
+        <v>29696</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>29696.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>36823.04</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>SYJ16L01</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Visor de Líquido 5/8" Roscable - Sanhua</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>31021</v>
+      <c r="F81" t="n">
+        <v>31348</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>31348.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>38871.52</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>MDF-A03-2H002</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Válvula Solenoide 1/4" 220V Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>38083</v>
-      </c>
+      <c r="F82" t="n">
+        <v>38485</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>38485.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>47721.40</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>MDF-A03-2L002</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Válvula Solenoide 1/4" 220V Rosca - Sanhua</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>37101</v>
-      </c>
+      <c r="F83" t="n">
+        <v>37493</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>37493.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>46491.32</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>SBV(M)-JA5YHSY-1-SA</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Válvula de Bola 5/8" (16mm) Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>34926</v>
+      <c r="F84" t="n">
+        <v>35295</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>35295.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>43765.80</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>SBV(M)-JA6YHSY-1-SA</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Válvula de Bola 3/4" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>46396</v>
+      <c r="F85" t="n">
+        <v>46886</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>46886.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>58138.64</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>SBV(M)-JA7YSHY-1-SA</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Válvula de Bola 7/8" (22mm) Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>49844</v>
+      <c r="F86" t="n">
+        <v>50371</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>50371.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>62460.04</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>YFQ-F00101-003</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Separador de Aceite 5/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>126988</v>
+      <c r="F87" t="n">
+        <v>128329</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>128329.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>159127.96</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>YFQ-F00101-004</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Separador de Aceite 7/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>142672</v>
+      <c r="F88" t="n">
+        <v>144179</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>144179.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>178781.96</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>YFQ-F00101-005</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Separador de Aceite 1-1/8" Soldable Sanhua</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>160689</v>
+      <c r="F89" t="n">
+        <v>162387</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>162387.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>201359.88</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>SQ-A2522G-000870</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Bobina para Válvula Inversora (220V-240V) Sanhua</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>9122</v>
+      <c r="F90" t="n">
+        <v>9218</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>9218.0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>11430.32</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>MDF-A03-3H004</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Válvula Solenoide 3/8" 220V Soldable - Sanhua</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>41471</v>
+      <c r="F91" t="n">
+        <v>41909</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>41909.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>51967.16</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>YCVS20-77GSHC-1</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 7/8"-22mm Angular Sanhua</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>52991</v>
+      <c r="F92" t="n">
+        <v>53551</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>53551.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>66403.24</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>YCVS26-99GSHC-1</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-1/8" Angular Sanhua</t>
         </is>
       </c>
-      <c r="C93" t="n">
-        <v>118246</v>
+      <c r="F93" t="n">
+        <v>119495</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>119495.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>148173.80</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>YCVS31-BBGSHC-1</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-3/8"-35mm Angular Sanhua</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>135394</v>
+      <c r="F94" t="n">
+        <v>136824</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>136824.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>169661.76</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>YCVS31-DDGSHC-1</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-5/8" Angular Sanhua</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>154832</v>
+      <c r="F95" t="n">
+        <v>156468</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>156468.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>194020.32</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>YCVSH20-77GSHC-1</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 7/8" Angular - Resorte Reforzado Sanhua</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>52991</v>
+      <c r="F96" t="n">
+        <v>53551</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>53551.0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>66403.24</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>YCVSH26-99GSHC-1</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-1/8" Angular Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C97" t="n">
-        <v>118246</v>
+      <c r="F97" t="n">
+        <v>119495</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>119495.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>148173.80</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>YCVSH31-BBGSHC-1</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-3/8"-35mm Angular Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>135394</v>
+      <c r="F98" t="n">
+        <v>136824</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>136824.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>169661.76</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>YCVSH31-DDGSHC-1</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1-5/8" Angular - Resorte Reforzado Sanhua</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>154984</v>
+      <c r="F99" t="n">
+        <v>156622</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>156622.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>194211.28</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>YCVS3H01</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 3/8" Lineal Sanhua</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>16935</v>
+      <c r="F100" t="n">
+        <v>17113</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>17113.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>21220.12</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>YCVS4H01</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1/2" Lineal Sanhua</t>
         </is>
       </c>
-      <c r="C101" t="n">
-        <v>13181</v>
+      <c r="F101" t="n">
+        <v>13320</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>13320.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>16516.80</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>YCVS5H03</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 5/8" - 16mm Lineal Sanhua</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>32766</v>
+      <c r="F102" t="n">
+        <v>33112</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>33112.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>41058.88</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>YCVS6H03</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 3/4" Lineal Sanhua</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>39130</v>
+      <c r="F103" t="n">
+        <v>39544</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>39544.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>49034.56</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>YCVS7H03</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 7/8" - 22mm Lineal Sanhua</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>47923</v>
+      <c r="F104" t="n">
+        <v>48429</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>48429.0</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>60051.96</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>YCVSH3H01</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 3/8" Lineal Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C105" t="n">
-        <v>10584</v>
+      <c r="F105" t="n">
+        <v>10696</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10696.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>13263.04</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>YCVSH4H01</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 1/2" Lineal Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v>21089</v>
+      <c r="F106" t="n">
+        <v>21312</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>21312.0</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>26426.88</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>YCVSH5H03</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 5/8" - 16mm Lineal - Resorte Reforzado Sanhua</t>
         </is>
       </c>
-      <c r="C107" t="n">
-        <v>20927</v>
+      <c r="F107" t="n">
+        <v>21148</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>21148.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>26223.52</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>YCVSH6H03</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 3/4" Lineal Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>39130</v>
+      <c r="F108" t="n">
+        <v>39544</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>39544.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>49034.56</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>YCVSH7H03</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>Válvula de Retención Tipo Pistón 7/8" - 22mm Lineal Sanhua- Resorte Reforzado</t>
         </is>
       </c>
-      <c r="C109" t="n">
-        <v>40778</v>
+      <c r="F109" t="n">
+        <v>41209</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>41209.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>51099.16</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>PSV01AL-S01</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>Presostato Simple de Baja Presión (Reset Automático) Sanhua</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v>58745</v>
+      <c r="F110" t="n">
+        <v>59365</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>59365.0</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>73612.60</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>PSV15AAL-S51</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>Presostato Dual (Alta y Baja) - Reset Automático Sanhua</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>87258</v>
+      <c r="F111" t="n">
+        <v>88180</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>88180.0</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>109343.20</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>Duna srl</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>PSV50AL-S51</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>Presostato Simple de Alta Presión (Reset Automático) Sanhua</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v>62566</v>
+      <c r="F112" t="n">
+        <v>63227</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>63227.0</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>78401.48</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>not_found</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Code not found in ProductSupplier</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/media/price_lists/duna_srl.xlsx
+++ b/media/price_lists/duna_srl.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>66938</v>
+        <v>66239</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -527,12 +527,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66938.0</t>
+          <t>66239.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>83003.12</t>
+          <t>82136.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>68029</v>
+        <v>67318</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>68029.0</t>
+          <t>67318.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>84355.96</t>
+          <t>83474.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>66940</v>
+        <v>66241</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -639,12 +639,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66940.0</t>
+          <t>66241.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>83005.60</t>
+          <t>82138.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>59145</v>
+        <v>58527</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59145.0</t>
+          <t>58527.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>73339.80</t>
+          <t>72573.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>68029</v>
+        <v>67318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -751,12 +751,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68029.0</t>
+          <t>67318.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>84355.96</t>
+          <t>83474.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -807,12 +807,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -863,12 +863,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -975,12 +975,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10609</v>
+        <v>10498</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10609.0</t>
+          <t>10498.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13155.16</t>
+          <t>13017.52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>68029</v>
+        <v>67318</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>68029.0</t>
+          <t>67318.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>84355.96</t>
+          <t>83474.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34452</v>
+        <v>34092</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34452.0</t>
+          <t>34092.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42720.48</t>
+          <t>42274.08</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>34588</v>
+        <v>34226</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34588.0</t>
+          <t>34226.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>42889.12</t>
+          <t>42440.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>35295</v>
+        <v>34926</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35295.0</t>
+          <t>34926.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43765.80</t>
+          <t>43308.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10810</v>
+        <v>10697</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10810.0</t>
+          <t>10697.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13404.40</t>
+          <t>13264.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14755</v>
+        <v>14601</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14755.0</t>
+          <t>14601.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18296.20</t>
+          <t>18105.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19000</v>
+        <v>18801</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19000.0</t>
+          <t>18801.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23560.00</t>
+          <t>23313.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>24849</v>
+        <v>24589</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24849.0</t>
+          <t>24589.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30812.76</t>
+          <t>30490.36</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>36711</v>
+        <v>36328</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>36711.0</t>
+          <t>36328.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45521.64</t>
+          <t>45046.72</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>74396</v>
+        <v>73618</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>74396.0</t>
+          <t>73618.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>92251.04</t>
+          <t>91286.32</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>80899</v>
+        <v>80053</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>80899.0</t>
+          <t>80053.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>100314.76</t>
+          <t>99265.72</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>171963</v>
+        <v>170166</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>171963.0</t>
+          <t>170166.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>213234.12</t>
+          <t>211005.84</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>38325</v>
+        <v>37924</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>38325.0</t>
+          <t>37924.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>47523.00</t>
+          <t>47025.76</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>58713</v>
+        <v>58099</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>58713.0</t>
+          <t>58099.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>72804.12</t>
+          <t>72042.76</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>50455</v>
+        <v>49927</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50455.0</t>
+          <t>49927.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>62564.20</t>
+          <t>61909.48</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>34656</v>
+        <v>34293</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>34656.0</t>
+          <t>34293.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>42973.44</t>
+          <t>42523.32</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>46854</v>
+        <v>46365</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46854.0</t>
+          <t>46365.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>58098.96</t>
+          <t>57492.60</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>67557</v>
+        <v>66851</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>67557.0</t>
+          <t>66851.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>83770.68</t>
+          <t>82895.24</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>108578</v>
+        <v>107443</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>108578.0</t>
+          <t>107443.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>134636.72</t>
+          <t>133229.32</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>91986</v>
+        <v>91024</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>91986.0</t>
+          <t>91024.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>114062.64</t>
+          <t>112869.76</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>94185</v>
+        <v>93200</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>94185.0</t>
+          <t>93200.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>116789.40</t>
+          <t>115568.00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>94907</v>
+        <v>93914</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>94907.0</t>
+          <t>93914.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>117684.68</t>
+          <t>116453.36</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>47993</v>
+        <v>47491</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47993.0</t>
+          <t>47491.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>59511.32</t>
+          <t>58888.84</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>26419</v>
+        <v>26143</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26419.0</t>
+          <t>26143.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>32759.56</t>
+          <t>32417.32</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26419</v>
+        <v>26143</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26419.0</t>
+          <t>26143.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>32759.56</t>
+          <t>32417.32</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>40987</v>
+        <v>40558</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40987.0</t>
+          <t>40558.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>50823.88</t>
+          <t>50291.92</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>138006</v>
+        <v>136563</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>138006.0</t>
+          <t>136563.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>171127.44</t>
+          <t>169338.12</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>139218</v>
+        <v>137762</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>139218.0</t>
+          <t>137762.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>172630.32</t>
+          <t>170824.88</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10148</v>
+        <v>10042</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10148.0</t>
+          <t>10042.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12583.52</t>
+          <t>12452.08</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>21910</v>
+        <v>21681</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21910.0</t>
+          <t>21681.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>27168.40</t>
+          <t>26884.44</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>17345</v>
+        <v>17164</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17345.0</t>
+          <t>17164.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21507.80</t>
+          <t>21283.36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>21966</v>
+        <v>21736</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21966.0</t>
+          <t>21736.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>27237.84</t>
+          <t>26952.64</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>17682</v>
+        <v>17497</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17682.0</t>
+          <t>17497.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>21925.68</t>
+          <t>21696.28</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22695</v>
+        <v>22457</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>22695.0</t>
+          <t>22457.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>28141.80</t>
+          <t>27846.68</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>18214</v>
+        <v>18024</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18214.0</t>
+          <t>18024.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22585.36</t>
+          <t>22349.76</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>23283</v>
+        <v>23040</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>23283.0</t>
+          <t>23040.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>28870.92</t>
+          <t>28569.60</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>18297</v>
+        <v>18106</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>18297.0</t>
+          <t>18106.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>22688.28</t>
+          <t>22451.44</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>24851</v>
+        <v>24591</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3259,12 +3259,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24851.0</t>
+          <t>24591.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30815.24</t>
+          <t>30492.84</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>18382</v>
+        <v>18190</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18382.0</t>
+          <t>18190.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>22793.68</t>
+          <t>22555.60</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>26699</v>
+        <v>26420</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>26699.0</t>
+          <t>26420.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>33106.76</t>
+          <t>32760.80</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>18466</v>
+        <v>18273</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18466.0</t>
+          <t>18273.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22897.84</t>
+          <t>22658.52</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>26981</v>
+        <v>26699</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26981.0</t>
+          <t>26699.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33456.44</t>
+          <t>33106.76</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>34290</v>
+        <v>33932</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>34290.0</t>
+          <t>33932.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>42519.60</t>
+          <t>42075.68</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>27708</v>
+        <v>27419</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>27708.0</t>
+          <t>27419.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>34357.92</t>
+          <t>33999.56</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>35971</v>
+        <v>35595</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3651,12 +3651,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>35971.0</t>
+          <t>35595.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>44604.04</t>
+          <t>44137.80</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>28521</v>
+        <v>28223</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>28521.0</t>
+          <t>28223.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>35366.04</t>
+          <t>34996.52</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>157435</v>
+        <v>155789</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>157435.0</t>
+          <t>155789.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>195219.40</t>
+          <t>193178.36</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>157083</v>
+        <v>155441</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>157083.0</t>
+          <t>155441.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>194782.92</t>
+          <t>192746.84</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>182565</v>
+        <v>180657</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>182565.0</t>
+          <t>180657.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>226380.60</t>
+          <t>224014.68</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>196632</v>
+        <v>194576</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3931,12 +3931,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>196632.0</t>
+          <t>194576.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>243823.68</t>
+          <t>241274.24</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>157435</v>
+        <v>155789</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>157435.0</t>
+          <t>155789.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>195219.40</t>
+          <t>193178.36</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>157435</v>
+        <v>155789</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>157435.0</t>
+          <t>155789.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>195219.40</t>
+          <t>193178.36</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>157435</v>
+        <v>155789</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>157435.0</t>
+          <t>155789.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>195219.40</t>
+          <t>193178.36</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>124656</v>
+        <v>123353</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>124656.0</t>
+          <t>123353.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>154573.44</t>
+          <t>152957.72</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>156607</v>
+        <v>154970</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>156607.0</t>
+          <t>154970.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>194192.68</t>
+          <t>192162.80</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>169664</v>
+        <v>167891</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>169664.0</t>
+          <t>167891.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>210383.36</t>
+          <t>208184.84</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>177284</v>
+        <v>175431</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>177284.0</t>
+          <t>175431.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>219832.16</t>
+          <t>217534.44</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>207029</v>
+        <v>204865</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>207029.0</t>
+          <t>204865.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>256715.96</t>
+          <t>254032.60</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>126794</v>
+        <v>125469</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>126794.0</t>
+          <t>125469.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>157224.56</t>
+          <t>155581.56</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>19053</v>
+        <v>18854</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>19053.0</t>
+          <t>18854.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>23625.72</t>
+          <t>23378.96</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>21406</v>
+        <v>21182</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>21406.0</t>
+          <t>21182.0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>26543.44</t>
+          <t>26265.68</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28296</v>
+        <v>28000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>28296.0</t>
+          <t>28000.0</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>35087.04</t>
+          <t>34720.00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>29754</v>
+        <v>29443</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>29754.0</t>
+          <t>29443.0</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>36894.96</t>
+          <t>36509.32</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>27486</v>
+        <v>27199</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>27486.0</t>
+          <t>27199.0</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>34082.64</t>
+          <t>33726.76</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>30151</v>
+        <v>29836</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>30151.0</t>
+          <t>29836.0</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>37387.24</t>
+          <t>36996.64</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>25944</v>
+        <v>25672</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25944.0</t>
+          <t>25672.0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>32170.56</t>
+          <t>31833.28</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>29696</v>
+        <v>29386</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>29386.0</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>36823.04</t>
+          <t>36438.64</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>31348</v>
+        <v>31021</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>31348.0</t>
+          <t>31021.0</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>38871.52</t>
+          <t>38466.04</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>38485</v>
+        <v>38083</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>38485.0</t>
+          <t>38083.0</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>47721.40</t>
+          <t>47222.92</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>37493</v>
+        <v>37101</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5027,12 +5027,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>37493.0</t>
+          <t>37101.0</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>46491.32</t>
+          <t>46005.24</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>35295</v>
+        <v>34926</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>35295.0</t>
+          <t>34926.0</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>43765.80</t>
+          <t>43308.24</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>46886</v>
+        <v>46396</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>46886.0</t>
+          <t>46396.0</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>58138.64</t>
+          <t>57531.04</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>50371</v>
+        <v>49844</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5191,12 +5191,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>50371.0</t>
+          <t>49844.0</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>62460.04</t>
+          <t>61806.56</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>128329</v>
+        <v>126988</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5247,12 +5247,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>128329.0</t>
+          <t>126988.0</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>159127.96</t>
+          <t>157465.12</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>144179</v>
+        <v>142672</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>144179.0</t>
+          <t>142672.0</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>178781.96</t>
+          <t>176913.28</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>162387</v>
+        <v>160689</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>162387.0</t>
+          <t>160689.0</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>201359.88</t>
+          <t>199254.36</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>9218</v>
+        <v>9122</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9218.0</t>
+          <t>9122.0</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>11430.32</t>
+          <t>11311.28</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>41909</v>
+        <v>41471</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5471,12 +5471,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>41909.0</t>
+          <t>41471.0</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>51967.16</t>
+          <t>51424.04</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>53551</v>
+        <v>52991</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>53551.0</t>
+          <t>52991.0</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>66403.24</t>
+          <t>65708.84</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>119495</v>
+        <v>118246</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>119495.0</t>
+          <t>118246.0</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>148173.80</t>
+          <t>146625.04</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>136824</v>
+        <v>135394</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>136824.0</t>
+          <t>135394.0</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>169661.76</t>
+          <t>167888.56</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>156468</v>
+        <v>154832</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>156468.0</t>
+          <t>154832.0</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>194020.32</t>
+          <t>191991.68</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>53551</v>
+        <v>52991</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>53551.0</t>
+          <t>52991.0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>66403.24</t>
+          <t>65708.84</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>119495</v>
+        <v>118246</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>119495.0</t>
+          <t>118246.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>148173.80</t>
+          <t>146625.04</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>136824</v>
+        <v>135394</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>136824.0</t>
+          <t>135394.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>169661.76</t>
+          <t>167888.56</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>156622</v>
+        <v>154984</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>156622.0</t>
+          <t>154984.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>194211.28</t>
+          <t>192180.16</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>17113</v>
+        <v>16935</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>17113.0</t>
+          <t>16935.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>21220.12</t>
+          <t>20999.40</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>13320</v>
+        <v>13181</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>13320.0</t>
+          <t>13181.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>16516.80</t>
+          <t>16344.44</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>33112</v>
+        <v>32766</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33112.0</t>
+          <t>32766.0</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>41058.88</t>
+          <t>40629.84</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>39544</v>
+        <v>39130</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6143,12 +6143,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>39544.0</t>
+          <t>39130.0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>49034.56</t>
+          <t>48521.20</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>48429</v>
+        <v>47923</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>48429.0</t>
+          <t>47923.0</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>60051.96</t>
+          <t>59424.52</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>10696</v>
+        <v>10584</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6255,12 +6255,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10696.0</t>
+          <t>10584.0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>13263.04</t>
+          <t>13124.16</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>21312</v>
+        <v>21089</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>21312.0</t>
+          <t>21089.0</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>26426.88</t>
+          <t>26150.36</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>21148</v>
+        <v>20927</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>21148.0</t>
+          <t>20927.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>26223.52</t>
+          <t>25949.48</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>39544</v>
+        <v>39130</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>39544.0</t>
+          <t>39130.0</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>49034.56</t>
+          <t>48521.20</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>41209</v>
+        <v>40778</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>41209.0</t>
+          <t>40778.0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>51099.16</t>
+          <t>50564.72</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>59365</v>
+        <v>58745</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>59365.0</t>
+          <t>58745.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>73612.60</t>
+          <t>72843.80</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>88180</v>
+        <v>87258</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6591,12 +6591,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>88180.0</t>
+          <t>87258.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>109343.20</t>
+          <t>108199.92</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>63227</v>
+        <v>62566</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>63227.0</t>
+          <t>62566.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78401.48</t>
+          <t>77581.84</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">

--- a/media/price_lists/duna_srl.xlsx
+++ b/media/price_lists/duna_srl.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>66239</v>
+        <v>65539</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -527,12 +527,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66239.0</t>
+          <t>65539.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>82136.36</t>
+          <t>81268.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>67318</v>
+        <v>66607</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>67318.0</t>
+          <t>66607.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>83474.32</t>
+          <t>82592.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>66241</v>
+        <v>65541</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -639,12 +639,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66241.0</t>
+          <t>65541.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>82138.84</t>
+          <t>81270.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>58527</v>
+        <v>57908</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58527.0</t>
+          <t>57908.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>72573.48</t>
+          <t>71805.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>67318</v>
+        <v>66607</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -751,12 +751,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67318.0</t>
+          <t>66607.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83474.32</t>
+          <t>82592.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -807,12 +807,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -863,12 +863,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -975,12 +975,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10498</v>
+        <v>10387</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10498.0</t>
+          <t>10387.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13017.52</t>
+          <t>12879.88</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67318</v>
+        <v>66607</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>67318.0</t>
+          <t>66607.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>83474.32</t>
+          <t>82592.68</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34092</v>
+        <v>33732</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34092.0</t>
+          <t>33732.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42274.08</t>
+          <t>41827.68</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>34226</v>
+        <v>33865</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34226.0</t>
+          <t>33865.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>42440.24</t>
+          <t>41992.60</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34926</v>
+        <v>34557</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34926.0</t>
+          <t>34557.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43308.24</t>
+          <t>42850.68</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10697</v>
+        <v>10584</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10697.0</t>
+          <t>10584.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13264.28</t>
+          <t>13124.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14601</v>
+        <v>14447</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14601.0</t>
+          <t>14447.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18105.24</t>
+          <t>17914.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18801</v>
+        <v>18602</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18801.0</t>
+          <t>18602.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23313.24</t>
+          <t>23066.48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>24589</v>
+        <v>24329</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24589.0</t>
+          <t>24329.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30490.36</t>
+          <t>30167.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>36328</v>
+        <v>35944</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>36328.0</t>
+          <t>35944.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45046.72</t>
+          <t>44570.56</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>73618</v>
+        <v>72841</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>73618.0</t>
+          <t>72841.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>91286.32</t>
+          <t>90322.84</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>80053</v>
+        <v>79207</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>80053.0</t>
+          <t>79207.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>99265.72</t>
+          <t>98216.68</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>170166</v>
+        <v>168368</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>170166.0</t>
+          <t>168368.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>211005.84</t>
+          <t>208776.32</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>37924</v>
+        <v>37524</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>37924.0</t>
+          <t>37524.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>47025.76</t>
+          <t>46529.76</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>58099</v>
+        <v>57485</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>58099.0</t>
+          <t>57485.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>72042.76</t>
+          <t>71281.40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>49927</v>
+        <v>49400</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>49927.0</t>
+          <t>49400.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>61909.48</t>
+          <t>61256.00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>34293</v>
+        <v>33931</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>34293.0</t>
+          <t>33931.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>42523.32</t>
+          <t>42074.44</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>46365</v>
+        <v>45875</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46365.0</t>
+          <t>45875.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>57492.60</t>
+          <t>56885.00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>66851</v>
+        <v>66145</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>66851.0</t>
+          <t>66145.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>82895.24</t>
+          <t>82019.80</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>107443</v>
+        <v>106309</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>107443.0</t>
+          <t>106309.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>133229.32</t>
+          <t>131823.16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>91024</v>
+        <v>90063</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>91024.0</t>
+          <t>90063.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>112869.76</t>
+          <t>111678.12</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>93200</v>
+        <v>92216</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>93200.0</t>
+          <t>92216.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>115568.00</t>
+          <t>114347.84</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>93914</v>
+        <v>92922</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>93914.0</t>
+          <t>92922.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>116453.36</t>
+          <t>115223.28</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>47491</v>
+        <v>46990</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47491.0</t>
+          <t>46990.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>58888.84</t>
+          <t>58267.60</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>26143</v>
+        <v>25866</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26143.0</t>
+          <t>25866.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>32417.32</t>
+          <t>32073.84</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26143</v>
+        <v>25866</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>26143.0</t>
+          <t>25866.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>32417.32</t>
+          <t>32073.84</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>40558</v>
+        <v>40130</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40558.0</t>
+          <t>40130.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>50291.92</t>
+          <t>49761.20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>136563</v>
+        <v>135120</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>136563.0</t>
+          <t>135120.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>169338.12</t>
+          <t>167548.80</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>137762</v>
+        <v>136307</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>137762.0</t>
+          <t>136307.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>170824.88</t>
+          <t>169020.68</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10042</v>
+        <v>9936</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10042.0</t>
+          <t>9936.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>12452.08</t>
+          <t>12320.64</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>21681</v>
+        <v>21452</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21681.0</t>
+          <t>21452.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26884.44</t>
+          <t>26600.48</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>17164</v>
+        <v>16983</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17164.0</t>
+          <t>16983.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21283.36</t>
+          <t>21058.92</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>21736</v>
+        <v>21507</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21736.0</t>
+          <t>21507.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>26952.64</t>
+          <t>26668.68</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>17497</v>
+        <v>17312</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2979,12 +2979,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17497.0</t>
+          <t>17312.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>21696.28</t>
+          <t>21466.88</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22457</v>
+        <v>22220</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>22457.0</t>
+          <t>22220.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27846.68</t>
+          <t>27552.80</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>18024</v>
+        <v>17833</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18024.0</t>
+          <t>17833.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22349.76</t>
+          <t>22112.92</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>23040</v>
+        <v>22796</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>23040.0</t>
+          <t>22796.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>28569.60</t>
+          <t>28267.04</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>18106</v>
+        <v>17915</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>18106.0</t>
+          <t>17915.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>22451.44</t>
+          <t>22214.60</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>24591</v>
+        <v>24331</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3259,12 +3259,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24591.0</t>
+          <t>24331.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30492.84</t>
+          <t>30170.44</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>18190</v>
+        <v>17997</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18190.0</t>
+          <t>17997.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>22555.60</t>
+          <t>22316.28</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>26420</v>
+        <v>26141</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>26420.0</t>
+          <t>26141.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>32760.80</t>
+          <t>32414.84</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>18273</v>
+        <v>18080</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18273.0</t>
+          <t>18080.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>22658.52</t>
+          <t>22419.20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>26699</v>
+        <v>26417</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26699.0</t>
+          <t>26417.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33106.76</t>
+          <t>32757.08</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>33932</v>
+        <v>33573</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>33932.0</t>
+          <t>33573.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>42075.68</t>
+          <t>41630.52</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>27419</v>
+        <v>27129</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>27419.0</t>
+          <t>27129.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>33999.56</t>
+          <t>33639.96</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>35595</v>
+        <v>35219</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3651,12 +3651,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>35595.0</t>
+          <t>35219.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>44137.80</t>
+          <t>43671.56</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>28223</v>
+        <v>27925</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>28223.0</t>
+          <t>27925.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>34996.52</t>
+          <t>34627.00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>155789</v>
+        <v>154144</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>155789.0</t>
+          <t>154144.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>193178.36</t>
+          <t>191138.56</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>155441</v>
+        <v>153799</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>155441.0</t>
+          <t>153799.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>192746.84</t>
+          <t>190710.76</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>180657</v>
+        <v>178749</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3875,12 +3875,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>180657.0</t>
+          <t>178749.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>224014.68</t>
+          <t>221648.76</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>194576</v>
+        <v>192521</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3931,12 +3931,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>194576.0</t>
+          <t>192521.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>241274.24</t>
+          <t>238726.04</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>155789</v>
+        <v>154144</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>155789.0</t>
+          <t>154144.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>193178.36</t>
+          <t>191138.56</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>155789</v>
+        <v>154144</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>155789.0</t>
+          <t>154144.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>193178.36</t>
+          <t>191138.56</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>155789</v>
+        <v>154144</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>155789.0</t>
+          <t>154144.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>193178.36</t>
+          <t>191138.56</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>123353</v>
+        <v>122050</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>123353.0</t>
+          <t>122050.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>152957.72</t>
+          <t>151342.00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>154970</v>
+        <v>153333</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>154970.0</t>
+          <t>153333.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>192162.80</t>
+          <t>190132.92</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>167891</v>
+        <v>166117</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>167891.0</t>
+          <t>166117.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>208184.84</t>
+          <t>205985.08</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>175431</v>
+        <v>173578</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>175431.0</t>
+          <t>173578.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>217534.44</t>
+          <t>215236.72</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>204865</v>
+        <v>202700</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>204865.0</t>
+          <t>202700.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>254032.60</t>
+          <t>251348.00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>125469</v>
+        <v>124143</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>125469.0</t>
+          <t>124143.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>155581.56</t>
+          <t>153937.32</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>18854</v>
+        <v>18655</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18854.0</t>
+          <t>18655.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>23378.96</t>
+          <t>23132.20</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>21182</v>
+        <v>20958</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>21182.0</t>
+          <t>20958.0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>26265.68</t>
+          <t>25987.92</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28000</v>
+        <v>27704</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>28000.0</t>
+          <t>27704.0</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>34720.00</t>
+          <t>34352.96</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>29443</v>
+        <v>29132</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>29443.0</t>
+          <t>29132.0</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>36509.32</t>
+          <t>36123.68</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>27199</v>
+        <v>26912</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>27199.0</t>
+          <t>26912.0</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>33726.76</t>
+          <t>33370.88</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>29836</v>
+        <v>29521</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>29836.0</t>
+          <t>29521.0</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>36996.64</t>
+          <t>36606.04</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>25672</v>
+        <v>25401</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25672.0</t>
+          <t>25401.0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>31833.28</t>
+          <t>31497.24</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>29386</v>
+        <v>29075</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>29386.0</t>
+          <t>29075.0</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>36438.64</t>
+          <t>36053.00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>31021</v>
+        <v>30693</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>31021.0</t>
+          <t>30693.0</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>38466.04</t>
+          <t>38059.32</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>38083</v>
+        <v>37681</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>38083.0</t>
+          <t>37681.0</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>47222.92</t>
+          <t>46724.44</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>37101</v>
+        <v>36709</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5027,12 +5027,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>37101.0</t>
+          <t>36709.0</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>46005.24</t>
+          <t>45519.16</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>34926</v>
+        <v>34557</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>34926.0</t>
+          <t>34557.0</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>43308.24</t>
+          <t>42850.68</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>46396</v>
+        <v>45906</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>46396.0</t>
+          <t>45906.0</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>57531.04</t>
+          <t>56923.44</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>49844</v>
+        <v>49318</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5191,12 +5191,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>49844.0</t>
+          <t>49318.0</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>61806.56</t>
+          <t>61154.32</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>126988</v>
+        <v>125646</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5247,12 +5247,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>126988.0</t>
+          <t>125646.0</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>157465.12</t>
+          <t>155801.04</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>142672</v>
+        <v>141164</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>142672.0</t>
+          <t>141164.0</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>176913.28</t>
+          <t>175043.36</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>160689</v>
+        <v>158992</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>160689.0</t>
+          <t>158992.0</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>199254.36</t>
+          <t>197150.08</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>9122</v>
+        <v>9026</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9122.0</t>
+          <t>9026.0</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>11311.28</t>
+          <t>11192.24</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>41471</v>
+        <v>41033</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5471,12 +5471,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>41471.0</t>
+          <t>41033.0</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>51424.04</t>
+          <t>50880.92</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>52991</v>
+        <v>52431</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>52991.0</t>
+          <t>52431.0</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>65708.84</t>
+          <t>65014.44</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>118246</v>
+        <v>116997</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>118246.0</t>
+          <t>116997.0</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>146625.04</t>
+          <t>145076.28</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>135394</v>
+        <v>133964</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>135394.0</t>
+          <t>133964.0</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>167888.56</t>
+          <t>166115.36</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>154832</v>
+        <v>153196</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>154832.0</t>
+          <t>153196.0</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>191991.68</t>
+          <t>189963.04</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>52991</v>
+        <v>52431</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5751,12 +5751,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>52991.0</t>
+          <t>52431.0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>65708.84</t>
+          <t>65014.44</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>118246</v>
+        <v>116997</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>118246.0</t>
+          <t>116997.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>146625.04</t>
+          <t>145076.28</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>135394</v>
+        <v>133964</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>135394.0</t>
+          <t>133964.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>167888.56</t>
+          <t>166115.36</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>154984</v>
+        <v>153347</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>154984.0</t>
+          <t>153347.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>192180.16</t>
+          <t>190150.28</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>16935</v>
+        <v>16756</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>16935.0</t>
+          <t>16756.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>20999.40</t>
+          <t>20777.44</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>13181</v>
+        <v>13041</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>13181.0</t>
+          <t>13041.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>16344.44</t>
+          <t>16170.84</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>32766</v>
+        <v>32420</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>32766.0</t>
+          <t>32420.0</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>40629.84</t>
+          <t>40200.80</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>39130</v>
+        <v>38717</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6143,12 +6143,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>39130.0</t>
+          <t>38717.0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>48521.20</t>
+          <t>48009.08</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>47923</v>
+        <v>47416</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>47923.0</t>
+          <t>47416.0</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>59424.52</t>
+          <t>58795.84</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>10584</v>
+        <v>10472</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6255,12 +6255,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10584.0</t>
+          <t>10472.0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>13124.16</t>
+          <t>12985.28</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>21089</v>
+        <v>20866</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>21089.0</t>
+          <t>20866.0</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>26150.36</t>
+          <t>25873.84</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>20927</v>
+        <v>20706</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6367,12 +6367,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20927.0</t>
+          <t>20706.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>25949.48</t>
+          <t>25675.44</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>39130</v>
+        <v>38717</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>39130.0</t>
+          <t>38717.0</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>48521.20</t>
+          <t>48009.08</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>40778</v>
+        <v>40347</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>40778.0</t>
+          <t>40347.0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>50564.72</t>
+          <t>50030.28</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>58745</v>
+        <v>58124</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>58745.0</t>
+          <t>58124.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>72843.80</t>
+          <t>72073.76</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>87258</v>
+        <v>86336</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6591,12 +6591,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>87258.0</t>
+          <t>86336.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>108199.92</t>
+          <t>107056.64</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>62566</v>
+        <v>61905</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>62566.0</t>
+          <t>61905.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77581.84</t>
+          <t>76762.20</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
